--- a/docs/files/exports/combined-combined-pricing-module-overview.xlsx
+++ b/docs/files/exports/combined-combined-pricing-module-overview.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Combined Web + App Pricing Module Overview</t>
+          <t>Pricing Module — Complete Overview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6,643 words</t>
+          <t>6,359 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Combined Web + App Pricing Module Overview Consolidated pricing module overview documenting all pricing tiers, methodology, and structure for both website and mobile application engagements. Scope: This document covers b...</t>
+          <t>Pricing Module — Complete Overview Comprehensive overview of the pricing module system for both Website and Mobile Application projects. Covers architecture, methodology, all parameter categories, and reference costs. Co...</t>
         </is>
       </c>
     </row>
